--- a/r4-ELGA-e-Diagnose-13-löschen-von-einzel-ressourcen/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-13-löschen-von-einzel-ressourcen/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:07:36+00:00</t>
+    <t>2026-09-08T12:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
